--- a/outputs/02_integrate_wos_verified_records/02_data/combined_ecotox_wos_harmonized.xlsx
+++ b/outputs/02_integrate_wos_verified_records/02_data/combined_ecotox_wos_harmonized.xlsx
@@ -9168,7 +9168,7 @@
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>OBrien 1988 reports total dissolved Cu LC95 values in 10^-6 M; the numeric Analysis_Point is therefore treated directly as umol Cu/L.</t>
+          <t>O'Brien et al. (1988), Table 1, p. 61: total dissolved Cu LC50 in 10^-6 M. Analysis_Point is used directly as umol Cu/L; LC95 and cupric-ion-activity columns are not used.</t>
         </is>
       </c>
       <c r="AH48" t="inlineStr">
@@ -9528,7 +9528,7 @@
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>OBrien 1988 reports total dissolved Cu LC97 values in 10^-6 M; the numeric Analysis_Point is therefore treated directly as umol Cu/L.</t>
+          <t>O'Brien et al. (1988), Table 1, p. 61: total dissolved Cu LC50 in 10^-6 M. Analysis_Point is used directly as umol Cu/L; LC95 and cupric-ion-activity columns are not used.</t>
         </is>
       </c>
       <c r="AH50" t="inlineStr">
@@ -9705,7 +9705,7 @@
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>OBrien 1988 reports total dissolved Cu LC98 values in 10^-6 M; the numeric Analysis_Point is therefore treated directly as umol Cu/L.</t>
+          <t>O'Brien et al. (1988), Table 1, p. 61: total dissolved Cu LC50 in 10^-6 M. Analysis_Point is used directly as umol Cu/L; LC95 and cupric-ion-activity columns are not used.</t>
         </is>
       </c>
       <c r="AH51" t="inlineStr">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>OBrien 1988 reports total dissolved Cu LC100 values in 10^-6 M; the numeric Analysis_Point is therefore treated directly as umol Cu/L.</t>
+          <t>O'Brien et al. (1988), Table 1, p. 61: total dissolved Cu LC50 in 10^-6 M. Analysis_Point is used directly as umol Cu/L; LC95 and cupric-ion-activity columns are not used.</t>
         </is>
       </c>
       <c r="AH53" t="inlineStr">
@@ -10793,7 +10793,7 @@
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>OBrien 1988 reports total dissolved Cu LC104 values in 10^-6 M; the numeric Analysis_Point is therefore treated directly as umol Cu/L.</t>
+          <t>O'Brien et al. (1988), Table 1, p. 61: total dissolved Cu LC50 in 10^-6 M. Analysis_Point is used directly as umol Cu/L; LC95 and cupric-ion-activity columns are not used.</t>
         </is>
       </c>
       <c r="AH57" t="inlineStr">
@@ -11158,7 +11158,7 @@
       </c>
       <c r="AG59" t="inlineStr">
         <is>
-          <t>OBrien 1988 reports total dissolved Cu LC106 values in 10^-6 M; the numeric Analysis_Point is therefore treated directly as umol Cu/L.</t>
+          <t>O'Brien et al. (1988), Table 1, p. 61: total dissolved Cu LC50 in 10^-6 M. Analysis_Point is used directly as umol Cu/L; LC95 and cupric-ion-activity columns are not used.</t>
         </is>
       </c>
       <c r="AH59" t="inlineStr">
@@ -11335,7 +11335,7 @@
       </c>
       <c r="AG60" t="inlineStr">
         <is>
-          <t>OBrien 1988 reports total dissolved Cu LC107 values in 10^-6 M; the numeric Analysis_Point is therefore treated directly as umol Cu/L.</t>
+          <t>O'Brien et al. (1988), Table 1, p. 61: total dissolved Cu LC50 in 10^-6 M. Analysis_Point is used directly as umol Cu/L; LC95 and cupric-ion-activity columns are not used.</t>
         </is>
       </c>
       <c r="AH60" t="inlineStr">
@@ -11512,7 +11512,7 @@
       </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>OBrien 1988 reports total dissolved Cu LC108 values in 10^-6 M; the numeric Analysis_Point is therefore treated directly as umol Cu/L.</t>
+          <t>O'Brien et al. (1988), Table 1, p. 61: total dissolved Cu LC50 in 10^-6 M. Analysis_Point is used directly as umol Cu/L; LC95 and cupric-ion-activity columns are not used.</t>
         </is>
       </c>
       <c r="AH61" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="AG64" t="inlineStr">
         <is>
-          <t>OBrien 1988 reports total dissolved Cu LC111 values in 10^-6 M; the numeric Analysis_Point is therefore treated directly as umol Cu/L.</t>
+          <t>O'Brien et al. (1988), Table 1, p. 61: total dissolved Cu LC50 in 10^-6 M. Analysis_Point is used directly as umol Cu/L; LC95 and cupric-ion-activity columns are not used.</t>
         </is>
       </c>
       <c r="AH64" t="inlineStr">
@@ -12231,7 +12231,7 @@
       </c>
       <c r="AG65" t="inlineStr">
         <is>
-          <t>OBrien 1988 reports total dissolved Cu LC112 values in 10^-6 M; the numeric Analysis_Point is therefore treated directly as umol Cu/L.</t>
+          <t>O'Brien et al. (1988), Table 1, p. 61: total dissolved Cu LC50 in 10^-6 M. Analysis_Point is used directly as umol Cu/L; LC95 and cupric-ion-activity columns are not used.</t>
         </is>
       </c>
       <c r="AH65" t="inlineStr">
@@ -12408,7 +12408,7 @@
       </c>
       <c r="AG66" t="inlineStr">
         <is>
-          <t>OBrien 1988 reports total dissolved Cu LC113 values in 10^-6 M; the numeric Analysis_Point is therefore treated directly as umol Cu/L.</t>
+          <t>O'Brien et al. (1988), Table 1, p. 61: total dissolved Cu LC50 in 10^-6 M. Analysis_Point is used directly as umol Cu/L; LC95 and cupric-ion-activity columns are not used.</t>
         </is>
       </c>
       <c r="AH66" t="inlineStr">
@@ -12585,7 +12585,7 @@
       </c>
       <c r="AG67" t="inlineStr">
         <is>
-          <t>OBrien 1988 reports total dissolved Cu LC114 values in 10^-6 M; the numeric Analysis_Point is therefore treated directly as umol Cu/L.</t>
+          <t>O'Brien et al. (1988), Table 1, p. 61: total dissolved Cu LC50 in 10^-6 M. Analysis_Point is used directly as umol Cu/L; LC95 and cupric-ion-activity columns are not used.</t>
         </is>
       </c>
       <c r="AH67" t="inlineStr">
@@ -12870,7 +12870,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Copepodite</t>
+          <t>Adult</t>
         </is>
       </c>
       <c r="J69">
@@ -12950,7 +12950,7 @@
       </c>
       <c r="AG69" t="inlineStr">
         <is>
-          <t>OBrien 1988 reports total dissolved Cu LC116 values in 10^-6 M; the numeric Analysis_Point is therefore treated directly as umol Cu/L.</t>
+          <t>O'Brien et al. (1988), Table 1, p. 61: total dissolved Cu LC50 in 10^-6 M. Analysis_Point is used directly as umol Cu/L; LC95 and cupric-ion-activity columns are not used.</t>
         </is>
       </c>
       <c r="AH69" t="inlineStr">
